--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Procedures3990304.xlsx
+++ b/docs/StructureDefinition-Procedures3990304.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
